--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119352004</v>
+        <v>120062180</v>
       </c>
       <c r="B78" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8480,38 +8480,54 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489021</v>
+        <v>488854</v>
       </c>
       <c r="R78" t="n">
-        <v>7085744</v>
+        <v>7085957</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8559,22 +8575,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119352000</v>
+        <v>120062181</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8587,21 +8603,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8611,10 +8627,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488961</v>
+        <v>488903</v>
       </c>
       <c r="R79" t="n">
-        <v>7085812</v>
+        <v>7085911</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8661,22 +8677,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062177</v>
+        <v>120062182</v>
       </c>
       <c r="B80" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8685,25 +8701,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8713,10 +8729,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489002</v>
+        <v>488900</v>
       </c>
       <c r="R80" t="n">
-        <v>7085931</v>
+        <v>7085951</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8775,10 +8791,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062181</v>
+        <v>120062174</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8787,25 +8803,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8815,10 +8831,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488903</v>
+        <v>488931</v>
       </c>
       <c r="R81" t="n">
-        <v>7085911</v>
+        <v>7085797</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8877,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062171</v>
+        <v>120062177</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>94311</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8889,46 +8905,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488880</v>
+        <v>489002</v>
       </c>
       <c r="R82" t="n">
-        <v>7085952</v>
+        <v>7085931</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8987,10 +8995,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062174</v>
+        <v>119352000</v>
       </c>
       <c r="B83" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8999,25 +9007,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9027,10 +9035,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488931</v>
+        <v>488961</v>
       </c>
       <c r="R83" t="n">
-        <v>7085797</v>
+        <v>7085812</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9077,22 +9085,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062180</v>
+        <v>119352004</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9101,54 +9109,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488854</v>
+        <v>489021</v>
       </c>
       <c r="R84" t="n">
-        <v>7085957</v>
+        <v>7085744</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9196,22 +9188,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062176</v>
+        <v>120062169</v>
       </c>
       <c r="B85" t="n">
-        <v>79608</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9224,21 +9216,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9248,10 +9240,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488931</v>
+        <v>488833</v>
       </c>
       <c r="R85" t="n">
-        <v>7085797</v>
+        <v>7085831</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9310,10 +9302,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062182</v>
+        <v>120062171</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9326,34 +9318,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488900</v>
+        <v>488880</v>
       </c>
       <c r="R86" t="n">
-        <v>7085951</v>
+        <v>7085952</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062169</v>
+        <v>120062176</v>
       </c>
       <c r="B87" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488833</v>
+        <v>488931</v>
       </c>
       <c r="R87" t="n">
-        <v>7085831</v>
+        <v>7085797</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8893,10 +8893,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062177</v>
+        <v>119352000</v>
       </c>
       <c r="B82" t="n">
-        <v>94311</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8905,25 +8905,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489002</v>
+        <v>488961</v>
       </c>
       <c r="R82" t="n">
-        <v>7085931</v>
+        <v>7085812</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8983,22 +8983,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119352000</v>
+        <v>120062177</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>94311</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9007,25 +9007,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488961</v>
+        <v>489002</v>
       </c>
       <c r="R83" t="n">
-        <v>7085812</v>
+        <v>7085931</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9085,12 +9085,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062180</v>
+        <v>120062181</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8480,54 +8480,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488854</v>
+        <v>488903</v>
       </c>
       <c r="R78" t="n">
-        <v>7085957</v>
+        <v>7085911</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8568,7 +8552,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8587,10 +8570,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062181</v>
+        <v>120062169</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8603,21 +8586,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8627,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488903</v>
+        <v>488833</v>
       </c>
       <c r="R79" t="n">
-        <v>7085911</v>
+        <v>7085831</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8791,10 +8774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062174</v>
+        <v>120062176</v>
       </c>
       <c r="B81" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8803,25 +8786,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8893,10 +8876,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119352000</v>
+        <v>120062177</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>94311</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8905,25 +8888,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8933,10 +8916,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488961</v>
+        <v>489002</v>
       </c>
       <c r="R82" t="n">
-        <v>7085812</v>
+        <v>7085931</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8983,22 +8966,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062177</v>
+        <v>119352004</v>
       </c>
       <c r="B83" t="n">
-        <v>94311</v>
+        <v>82305</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9007,25 +8990,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9035,10 +9018,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489002</v>
+        <v>489021</v>
       </c>
       <c r="R83" t="n">
-        <v>7085931</v>
+        <v>7085744</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9079,28 +9062,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119352004</v>
+        <v>119352000</v>
       </c>
       <c r="B84" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9113,21 +9097,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9137,10 +9121,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489021</v>
+        <v>488961</v>
       </c>
       <c r="R84" t="n">
-        <v>7085744</v>
+        <v>7085812</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9181,7 +9165,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9200,10 +9183,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062169</v>
+        <v>120062174</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9212,25 +9195,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9240,10 +9223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488833</v>
+        <v>488931</v>
       </c>
       <c r="R85" t="n">
-        <v>7085831</v>
+        <v>7085797</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9412,10 +9395,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062176</v>
+        <v>120062180</v>
       </c>
       <c r="B87" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9424,38 +9407,54 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488931</v>
+        <v>488854</v>
       </c>
       <c r="R87" t="n">
-        <v>7085797</v>
+        <v>7085957</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9496,6 +9495,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062181</v>
+        <v>119352004</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,21 +8484,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488903</v>
+        <v>489021</v>
       </c>
       <c r="R78" t="n">
-        <v>7085911</v>
+        <v>7085744</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8552,28 +8552,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062169</v>
+        <v>120062182</v>
       </c>
       <c r="B79" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8586,21 +8587,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8610,10 +8611,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488833</v>
+        <v>488900</v>
       </c>
       <c r="R79" t="n">
-        <v>7085831</v>
+        <v>7085951</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8665,17 +8666,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062182</v>
+        <v>120062171</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,34 +8689,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488900</v>
+        <v>488880</v>
       </c>
       <c r="R80" t="n">
-        <v>7085951</v>
+        <v>7085952</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8767,17 +8776,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062176</v>
+        <v>120062180</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8786,38 +8795,54 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488931</v>
+        <v>488854</v>
       </c>
       <c r="R81" t="n">
-        <v>7085797</v>
+        <v>7085957</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8858,6 +8883,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8869,7 +8895,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8971,17 +8997,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119352004</v>
+        <v>120062169</v>
       </c>
       <c r="B83" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8994,21 +9020,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9018,10 +9044,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489021</v>
+        <v>488833</v>
       </c>
       <c r="R83" t="n">
-        <v>7085744</v>
+        <v>7085831</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9062,29 +9088,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119352000</v>
+        <v>120062181</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9097,21 +9122,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9121,10 +9146,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488961</v>
+        <v>488903</v>
       </c>
       <c r="R84" t="n">
-        <v>7085812</v>
+        <v>7085911</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9171,22 +9196,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062174</v>
+        <v>120062176</v>
       </c>
       <c r="B85" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9195,25 +9220,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9278,14 +9303,14 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062171</v>
+        <v>119352000</v>
       </c>
       <c r="B86" t="n">
         <v>57310</v>
@@ -9319,24 +9344,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488880</v>
+        <v>488961</v>
       </c>
       <c r="R86" t="n">
-        <v>7085952</v>
+        <v>7085812</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9383,22 +9400,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062180</v>
+        <v>120062174</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9407,54 +9424,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488854</v>
+        <v>488931</v>
       </c>
       <c r="R87" t="n">
-        <v>7085957</v>
+        <v>7085797</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9495,7 +9496,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -9004,10 +9004,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062169</v>
+        <v>120062176</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
+        <v>79608</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9020,21 +9020,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488833</v>
+        <v>488931</v>
       </c>
       <c r="R83" t="n">
-        <v>7085831</v>
+        <v>7085797</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9099,17 +9099,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062181</v>
+        <v>120062169</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9122,21 +9122,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9146,10 +9146,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488903</v>
+        <v>488833</v>
       </c>
       <c r="R84" t="n">
-        <v>7085911</v>
+        <v>7085831</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062176</v>
+        <v>120062181</v>
       </c>
       <c r="B85" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9224,21 +9224,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488931</v>
+        <v>488903</v>
       </c>
       <c r="R85" t="n">
-        <v>7085797</v>
+        <v>7085911</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062171</v>
+        <v>120062180</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8685,35 +8685,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8721,10 +8729,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488880</v>
+        <v>488854</v>
       </c>
       <c r="R80" t="n">
-        <v>7085952</v>
+        <v>7085957</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8765,6 +8773,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8783,10 +8792,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062180</v>
+        <v>120062171</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8795,43 +8804,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8839,10 +8840,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488854</v>
+        <v>488880</v>
       </c>
       <c r="R81" t="n">
-        <v>7085957</v>
+        <v>7085952</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8883,7 +8884,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9004,10 +9004,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062176</v>
+        <v>120062169</v>
       </c>
       <c r="B83" t="n">
-        <v>79608</v>
+        <v>90562</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9020,21 +9020,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488931</v>
+        <v>488833</v>
       </c>
       <c r="R83" t="n">
-        <v>7085797</v>
+        <v>7085831</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9099,17 +9099,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062169</v>
+        <v>120062181</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9122,21 +9122,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9146,10 +9146,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488833</v>
+        <v>488903</v>
       </c>
       <c r="R84" t="n">
-        <v>7085831</v>
+        <v>7085911</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062181</v>
+        <v>120062176</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9224,21 +9224,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488903</v>
+        <v>488931</v>
       </c>
       <c r="R85" t="n">
-        <v>7085911</v>
+        <v>7085797</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062180</v>
+        <v>120062171</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8685,43 +8685,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8729,10 +8721,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488854</v>
+        <v>488880</v>
       </c>
       <c r="R80" t="n">
-        <v>7085957</v>
+        <v>7085952</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8773,7 +8765,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8792,10 +8783,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062171</v>
+        <v>120062180</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8804,35 +8795,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8840,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488880</v>
+        <v>488854</v>
       </c>
       <c r="R81" t="n">
-        <v>7085952</v>
+        <v>7085957</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8884,6 +8883,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -9004,10 +9004,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062169</v>
+        <v>120062181</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9020,21 +9020,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488833</v>
+        <v>488903</v>
       </c>
       <c r="R83" t="n">
-        <v>7085831</v>
+        <v>7085911</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9099,17 +9099,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062181</v>
+        <v>120062176</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9122,21 +9122,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9146,10 +9146,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488903</v>
+        <v>488931</v>
       </c>
       <c r="R84" t="n">
-        <v>7085911</v>
+        <v>7085797</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9208,10 +9208,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062176</v>
+        <v>120062169</v>
       </c>
       <c r="B85" t="n">
-        <v>79608</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9224,21 +9224,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488931</v>
+        <v>488833</v>
       </c>
       <c r="R85" t="n">
-        <v>7085797</v>
+        <v>7085831</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119352004</v>
+        <v>120062171</v>
       </c>
       <c r="B78" t="n">
-        <v>82305</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,34 +8484,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>489021</v>
+        <v>488880</v>
       </c>
       <c r="R78" t="n">
-        <v>7085744</v>
+        <v>7085952</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8552,19 +8560,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8574,7 +8581,7 @@
         <v>120062182</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8666,17 +8673,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062171</v>
+        <v>120062174</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79652</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8685,46 +8692,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488880</v>
+        <v>488931</v>
       </c>
       <c r="R80" t="n">
-        <v>7085952</v>
+        <v>7085797</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8776,17 +8775,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062180</v>
+        <v>119352000</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8795,54 +8794,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488854</v>
+        <v>488961</v>
       </c>
       <c r="R81" t="n">
-        <v>7085957</v>
+        <v>7085812</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8883,29 +8866,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062177</v>
+        <v>120062169</v>
       </c>
       <c r="B82" t="n">
-        <v>94311</v>
+        <v>90580</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8914,25 +8896,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8942,10 +8924,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>489002</v>
+        <v>488833</v>
       </c>
       <c r="R82" t="n">
-        <v>7085931</v>
+        <v>7085831</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8997,17 +8979,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062181</v>
+        <v>120062176</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9020,21 +9002,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9044,10 +9026,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488903</v>
+        <v>488931</v>
       </c>
       <c r="R83" t="n">
-        <v>7085911</v>
+        <v>7085797</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9099,17 +9081,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062176</v>
+        <v>119352004</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>82321</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9122,21 +9104,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9146,10 +9128,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488931</v>
+        <v>489021</v>
       </c>
       <c r="R84" t="n">
-        <v>7085797</v>
+        <v>7085744</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9190,28 +9172,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062169</v>
+        <v>120062181</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9224,21 +9207,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9248,10 +9231,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488833</v>
+        <v>488903</v>
       </c>
       <c r="R85" t="n">
-        <v>7085831</v>
+        <v>7085911</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9303,17 +9286,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119352000</v>
+        <v>120062180</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9322,38 +9305,54 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488961</v>
+        <v>488854</v>
       </c>
       <c r="R86" t="n">
-        <v>7085812</v>
+        <v>7085957</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9394,28 +9393,29 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062174</v>
+        <v>120062177</v>
       </c>
       <c r="B87" t="n">
-        <v>79636</v>
+        <v>94334</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488931</v>
+        <v>489002</v>
       </c>
       <c r="R87" t="n">
-        <v>7085797</v>
+        <v>7085931</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elias Blad, Iris Elmér, Erik Christiansson, Nora Toftgård Shahnavaz, Modi Hellsing, Karin Andersson, Astrid Blomberg, Janka Réthi, Karla Alfaro Gripe, Johan Thulin, Tore Dahlberg, Filippa Paperin, Elvira Klang</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062171</v>
+        <v>120062176</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,42 +8484,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488880</v>
+        <v>488931</v>
       </c>
       <c r="R78" t="n">
-        <v>7085952</v>
+        <v>7085797</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8578,10 +8570,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062182</v>
+        <v>119352000</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8594,21 +8586,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8618,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488900</v>
+        <v>488961</v>
       </c>
       <c r="R79" t="n">
-        <v>7085951</v>
+        <v>7085812</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8668,22 +8660,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062174</v>
+        <v>120062177</v>
       </c>
       <c r="B80" t="n">
-        <v>79652</v>
+        <v>94334</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8696,21 +8688,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8720,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488931</v>
+        <v>489002</v>
       </c>
       <c r="R80" t="n">
-        <v>7085797</v>
+        <v>7085931</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8782,10 +8774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119352000</v>
+        <v>120062169</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8798,21 +8790,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8822,10 +8814,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488961</v>
+        <v>488833</v>
       </c>
       <c r="R81" t="n">
-        <v>7085812</v>
+        <v>7085831</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8872,22 +8864,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062169</v>
+        <v>120062181</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8900,21 +8892,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8924,10 +8916,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488833</v>
+        <v>488903</v>
       </c>
       <c r="R82" t="n">
-        <v>7085831</v>
+        <v>7085911</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8986,10 +8978,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062176</v>
+        <v>120062171</v>
       </c>
       <c r="B83" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9002,34 +8994,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488931</v>
+        <v>488880</v>
       </c>
       <c r="R83" t="n">
-        <v>7085797</v>
+        <v>7085952</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9088,10 +9088,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119352004</v>
+        <v>120062182</v>
       </c>
       <c r="B84" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9104,21 +9104,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9128,10 +9128,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>489021</v>
+        <v>488900</v>
       </c>
       <c r="R84" t="n">
-        <v>7085744</v>
+        <v>7085951</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9172,29 +9172,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062181</v>
+        <v>119352004</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9207,21 +9206,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9231,10 +9230,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488903</v>
+        <v>489021</v>
       </c>
       <c r="R85" t="n">
-        <v>7085911</v>
+        <v>7085744</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9275,28 +9274,29 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062180</v>
+        <v>120062174</v>
       </c>
       <c r="B86" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9305,54 +9305,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488854</v>
+        <v>488931</v>
       </c>
       <c r="R86" t="n">
-        <v>7085957</v>
+        <v>7085797</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,7 +9377,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9412,10 +9395,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062177</v>
+        <v>120062180</v>
       </c>
       <c r="B87" t="n">
-        <v>94334</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9424,38 +9407,54 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489002</v>
+        <v>488854</v>
       </c>
       <c r="R87" t="n">
-        <v>7085931</v>
+        <v>7085957</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9496,6 +9495,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8570,10 +8570,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119352000</v>
+        <v>120062177</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>94334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8582,25 +8582,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488961</v>
+        <v>489002</v>
       </c>
       <c r="R79" t="n">
-        <v>7085812</v>
+        <v>7085931</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8660,22 +8660,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062177</v>
+        <v>120062169</v>
       </c>
       <c r="B80" t="n">
-        <v>94334</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8684,25 +8684,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489002</v>
+        <v>488833</v>
       </c>
       <c r="R80" t="n">
-        <v>7085931</v>
+        <v>7085831</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8774,10 +8774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062169</v>
+        <v>119352000</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488833</v>
+        <v>488961</v>
       </c>
       <c r="R81" t="n">
-        <v>7085831</v>
+        <v>7085812</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8864,12 +8864,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8672,10 +8672,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062169</v>
+        <v>119352000</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,21 +8688,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488833</v>
+        <v>488961</v>
       </c>
       <c r="R80" t="n">
-        <v>7085831</v>
+        <v>7085812</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8762,22 +8762,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119352000</v>
+        <v>120062169</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488961</v>
+        <v>488833</v>
       </c>
       <c r="R81" t="n">
-        <v>7085812</v>
+        <v>7085831</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8864,22 +8864,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062181</v>
+        <v>120062180</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8888,38 +8888,54 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488903</v>
+        <v>488854</v>
       </c>
       <c r="R82" t="n">
-        <v>7085911</v>
+        <v>7085957</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8960,6 +8976,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8978,10 +8995,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062171</v>
+        <v>120062182</v>
       </c>
       <c r="B83" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8994,42 +9011,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488880</v>
+        <v>488900</v>
       </c>
       <c r="R83" t="n">
-        <v>7085952</v>
+        <v>7085951</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9088,10 +9097,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062182</v>
+        <v>120062171</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9104,34 +9113,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488900</v>
+        <v>488880</v>
       </c>
       <c r="R84" t="n">
-        <v>7085951</v>
+        <v>7085952</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9190,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119352004</v>
+        <v>120062174</v>
       </c>
       <c r="B85" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9202,25 +9219,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9230,10 +9247,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489021</v>
+        <v>488931</v>
       </c>
       <c r="R85" t="n">
-        <v>7085744</v>
+        <v>7085797</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9274,29 +9291,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062174</v>
+        <v>119352004</v>
       </c>
       <c r="B86" t="n">
-        <v>79652</v>
+        <v>82321</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9305,25 +9321,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9333,10 +9349,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488931</v>
+        <v>489021</v>
       </c>
       <c r="R86" t="n">
-        <v>7085797</v>
+        <v>7085744</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9377,28 +9393,29 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062180</v>
+        <v>120062181</v>
       </c>
       <c r="B87" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9407,54 +9424,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488854</v>
+        <v>488903</v>
       </c>
       <c r="R87" t="n">
-        <v>7085957</v>
+        <v>7085911</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9495,7 +9496,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062176</v>
+        <v>120062180</v>
       </c>
       <c r="B78" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8480,38 +8480,54 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488931</v>
+        <v>488854</v>
       </c>
       <c r="R78" t="n">
-        <v>7085797</v>
+        <v>7085957</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8552,6 +8568,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8570,10 +8587,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062177</v>
+        <v>120062171</v>
       </c>
       <c r="B79" t="n">
-        <v>94334</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8582,38 +8599,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>489002</v>
+        <v>488880</v>
       </c>
       <c r="R79" t="n">
-        <v>7085931</v>
+        <v>7085952</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8672,10 +8697,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119352000</v>
+        <v>120062182</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,21 +8713,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8712,10 +8737,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488961</v>
+        <v>488900</v>
       </c>
       <c r="R80" t="n">
-        <v>7085812</v>
+        <v>7085951</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8762,22 +8787,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062169</v>
+        <v>119352000</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8790,21 +8815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8814,10 +8839,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488833</v>
+        <v>488961</v>
       </c>
       <c r="R81" t="n">
-        <v>7085831</v>
+        <v>7085812</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8864,22 +8889,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062180</v>
+        <v>120062176</v>
       </c>
       <c r="B82" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8888,54 +8913,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488854</v>
+        <v>488931</v>
       </c>
       <c r="R82" t="n">
-        <v>7085957</v>
+        <v>7085797</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8976,7 +8985,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8995,10 +9003,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062182</v>
+        <v>120062169</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9011,21 +9019,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9035,10 +9043,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488900</v>
+        <v>488833</v>
       </c>
       <c r="R83" t="n">
-        <v>7085951</v>
+        <v>7085831</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9097,10 +9105,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062171</v>
+        <v>120062174</v>
       </c>
       <c r="B84" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9109,46 +9117,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488880</v>
+        <v>488931</v>
       </c>
       <c r="R84" t="n">
-        <v>7085952</v>
+        <v>7085797</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062174</v>
+        <v>119352004</v>
       </c>
       <c r="B85" t="n">
-        <v>79652</v>
+        <v>82321</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9219,25 +9219,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488931</v>
+        <v>489021</v>
       </c>
       <c r="R85" t="n">
-        <v>7085797</v>
+        <v>7085744</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9291,28 +9291,29 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119352004</v>
+        <v>120062177</v>
       </c>
       <c r="B86" t="n">
-        <v>82321</v>
+        <v>94334</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9321,25 +9322,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9349,10 +9350,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489021</v>
+        <v>489002</v>
       </c>
       <c r="R86" t="n">
-        <v>7085744</v>
+        <v>7085931</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,19 +9394,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062180</v>
+        <v>120062182</v>
       </c>
       <c r="B78" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8480,54 +8480,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488854</v>
+        <v>488900</v>
       </c>
       <c r="R78" t="n">
-        <v>7085957</v>
+        <v>7085951</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8568,7 +8552,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8587,7 +8570,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062171</v>
+        <v>119352000</v>
       </c>
       <c r="B79" t="n">
         <v>57320</v>
@@ -8621,24 +8604,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488880</v>
+        <v>488961</v>
       </c>
       <c r="R79" t="n">
-        <v>7085952</v>
+        <v>7085812</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8685,22 +8660,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062182</v>
+        <v>119352004</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8713,21 +8688,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8737,10 +8712,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488900</v>
+        <v>489021</v>
       </c>
       <c r="R80" t="n">
-        <v>7085951</v>
+        <v>7085744</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8781,28 +8756,29 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119352000</v>
+        <v>120062174</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8811,25 +8787,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8839,10 +8815,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488961</v>
+        <v>488931</v>
       </c>
       <c r="R81" t="n">
-        <v>7085812</v>
+        <v>7085797</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8889,22 +8865,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062176</v>
+        <v>120062171</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8917,34 +8893,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488931</v>
+        <v>488880</v>
       </c>
       <c r="R82" t="n">
-        <v>7085797</v>
+        <v>7085952</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9105,10 +9089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062174</v>
+        <v>120062176</v>
       </c>
       <c r="B84" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9117,25 +9101,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9207,10 +9191,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119352004</v>
+        <v>120062180</v>
       </c>
       <c r="B85" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9219,38 +9203,54 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>489021</v>
+        <v>488854</v>
       </c>
       <c r="R85" t="n">
-        <v>7085744</v>
+        <v>7085957</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9298,22 +9298,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062177</v>
+        <v>120062181</v>
       </c>
       <c r="B86" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9322,25 +9322,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>489002</v>
+        <v>488903</v>
       </c>
       <c r="R86" t="n">
-        <v>7085931</v>
+        <v>7085911</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062181</v>
+        <v>120062177</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9424,25 +9424,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488903</v>
+        <v>489002</v>
       </c>
       <c r="R87" t="n">
-        <v>7085911</v>
+        <v>7085931</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120062182</v>
+        <v>119352000</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,21 +8484,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488900</v>
+        <v>488961</v>
       </c>
       <c r="R78" t="n">
-        <v>7085951</v>
+        <v>7085812</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8558,22 +8558,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119352000</v>
+        <v>120062182</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8586,21 +8586,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488961</v>
+        <v>488900</v>
       </c>
       <c r="R79" t="n">
-        <v>7085812</v>
+        <v>7085951</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8660,12 +8660,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8672,10 +8672,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119352004</v>
+        <v>120062171</v>
       </c>
       <c r="B80" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,34 +8688,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>489021</v>
+        <v>488880</v>
       </c>
       <c r="R80" t="n">
-        <v>7085744</v>
+        <v>7085952</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8756,29 +8764,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120062174</v>
+        <v>119352004</v>
       </c>
       <c r="B81" t="n">
-        <v>79652</v>
+        <v>82321</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8787,25 +8794,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8815,10 +8822,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488931</v>
+        <v>489021</v>
       </c>
       <c r="R81" t="n">
-        <v>7085797</v>
+        <v>7085744</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8859,28 +8866,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062171</v>
+        <v>120062169</v>
       </c>
       <c r="B82" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8893,42 +8901,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488880</v>
+        <v>488833</v>
       </c>
       <c r="R82" t="n">
-        <v>7085952</v>
+        <v>7085831</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062169</v>
+        <v>120062177</v>
       </c>
       <c r="B83" t="n">
-        <v>90580</v>
+        <v>94334</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8999,25 +8999,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488833</v>
+        <v>489002</v>
       </c>
       <c r="R83" t="n">
-        <v>7085831</v>
+        <v>7085931</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062180</v>
+        <v>120062181</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9203,54 +9203,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488854</v>
+        <v>488903</v>
       </c>
       <c r="R85" t="n">
-        <v>7085957</v>
+        <v>7085911</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9291,7 +9275,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9310,10 +9293,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062181</v>
+        <v>120062180</v>
       </c>
       <c r="B86" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9322,38 +9305,54 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488903</v>
+        <v>488854</v>
       </c>
       <c r="R86" t="n">
-        <v>7085911</v>
+        <v>7085957</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9394,6 +9393,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062177</v>
+        <v>120062174</v>
       </c>
       <c r="B87" t="n">
-        <v>94334</v>
+        <v>79652</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489002</v>
+        <v>488931</v>
       </c>
       <c r="R87" t="n">
-        <v>7085931</v>
+        <v>7085797</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>

--- a/artfynd/A 27595-2024 artfynd.xlsx
+++ b/artfynd/A 27595-2024 artfynd.xlsx
@@ -8468,10 +8468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119352000</v>
+        <v>119352004</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8484,21 +8484,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488961</v>
+        <v>489021</v>
       </c>
       <c r="R78" t="n">
-        <v>7085812</v>
+        <v>7085744</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8552,6 +8552,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8570,10 +8571,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120062182</v>
+        <v>120062177</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8582,25 +8583,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8610,10 +8611,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488900</v>
+        <v>489002</v>
       </c>
       <c r="R79" t="n">
-        <v>7085951</v>
+        <v>7085931</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8672,7 +8673,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120062171</v>
+        <v>119352000</v>
       </c>
       <c r="B80" t="n">
         <v>57320</v>
@@ -8706,24 +8707,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488880</v>
+        <v>488961</v>
       </c>
       <c r="R80" t="n">
-        <v>7085952</v>
+        <v>7085812</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8770,22 +8763,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
+          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119352004</v>
+        <v>120062171</v>
       </c>
       <c r="B81" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8798,34 +8791,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>489021</v>
+        <v>488880</v>
       </c>
       <c r="R81" t="n">
-        <v>7085744</v>
+        <v>7085952</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8866,29 +8867,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Blad, Elicia Olsson, Tore Dahlberg, Elvira Klang, Erik Christiansson, Iris Elmér, Janka Réthi, Johan Thulin, Karin Andersson, Karla Alfaro Gripe, Malte Lindberg, Modi Hellsing, Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Elvira Klang, Filippa Paperin, Tore Dahlberg, Johan Thulin, Karla Alfaro Gripe, Janka Réthi, Astrid Blomberg, Karin Andersson, Modi Hellsing, Nora Toftgård Shahnavaz, Erik Christiansson, Iris Elmér, Elias Blad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120062169</v>
+        <v>120062181</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488833</v>
+        <v>488903</v>
       </c>
       <c r="R82" t="n">
-        <v>7085831</v>
+        <v>7085911</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120062177</v>
+        <v>120062174</v>
       </c>
       <c r="B83" t="n">
-        <v>94334</v>
+        <v>79652</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9003,21 +9003,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>489002</v>
+        <v>488931</v>
       </c>
       <c r="R83" t="n">
-        <v>7085931</v>
+        <v>7085797</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120062176</v>
+        <v>120062169</v>
       </c>
       <c r="B84" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488931</v>
+        <v>488833</v>
       </c>
       <c r="R84" t="n">
-        <v>7085797</v>
+        <v>7085831</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120062181</v>
+        <v>120062176</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9207,21 +9207,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488903</v>
+        <v>488931</v>
       </c>
       <c r="R85" t="n">
-        <v>7085911</v>
+        <v>7085797</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9293,10 +9293,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120062180</v>
+        <v>120062182</v>
       </c>
       <c r="B86" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9305,54 +9305,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488854</v>
+        <v>488900</v>
       </c>
       <c r="R86" t="n">
-        <v>7085957</v>
+        <v>7085951</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9393,7 +9377,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9412,10 +9395,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120062174</v>
+        <v>120062180</v>
       </c>
       <c r="B87" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9424,38 +9407,54 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Väster-Lillsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488931</v>
+        <v>488854</v>
       </c>
       <c r="R87" t="n">
-        <v>7085797</v>
+        <v>7085957</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9496,6 +9495,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
